--- a/data/derived_outputs/nrc_pure_emotion_words_translated.xlsx
+++ b/data/derived_outputs/nrc_pure_emotion_words_translated.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>固有 VADER 极性 (Intrinsic Polarity)</t>
+          <t>固有 VADER 得分 (-4.0 to +4.0)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -476,31 +476,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>friendly</t>
+          <t>professional</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>友好的/热情的</t>
+          <t>专业严谨的</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>friendly (友好的/热情的)</t>
+          <t>professional (专业严谨的)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3271</v>
+        <v>2056</v>
       </c>
       <c r="F2" t="n">
-        <v>4.942</v>
+        <v>4.95</v>
       </c>
       <c r="G2" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -510,31 +510,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>professional</t>
+          <t>friendly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>专业严谨的</t>
+          <t>友好的/热情的</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>professional (专业严谨的)</t>
+          <t>friendly (友好的/热情的)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2056</v>
+        <v>3271</v>
       </c>
       <c r="F3" t="n">
-        <v>4.95</v>
+        <v>4.942</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
         <v>4.933</v>
       </c>
       <c r="G4" t="n">
-        <v>0.45</v>
+        <v>1.8</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -612,27 +612,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>fun</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>优异卓越的</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>excellent (优异卓越的)</t>
+          <t>fun (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2475</v>
+        <v>1802</v>
       </c>
       <c r="F6" t="n">
-        <v>4.956</v>
+        <v>4.951</v>
       </c>
       <c r="G6" t="n">
-        <v>0.675</v>
+        <v>2.3</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>recommend</t>
+          <t>facts</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -656,17 +656,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>recommend (情绪与感知词汇)</t>
+          <t>facts (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5998</v>
+        <v>317</v>
       </c>
       <c r="F7" t="n">
-        <v>4.945</v>
+        <v>4.909</v>
       </c>
       <c r="G7" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -680,27 +680,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fun</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>优异卓越的</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>fun (情绪与感知词汇)</t>
+          <t>excellent (优异卓越的)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1802</v>
+        <v>2475</v>
       </c>
       <c r="F8" t="n">
-        <v>4.951</v>
+        <v>4.956</v>
       </c>
       <c r="G8" t="n">
-        <v>0.575</v>
+        <v>2.7</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>facts</t>
+          <t>recommend</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>facts (情绪与感知词汇)</t>
+          <t>recommend (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>317</v>
+        <v>5998</v>
       </c>
       <c r="F9" t="n">
-        <v>4.909</v>
+        <v>4.945</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
         <v>4.92</v>
       </c>
       <c r="G10" t="n">
-        <v>0.225</v>
+        <v>0.9</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -782,31 +782,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>spectacular</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>壮观震撼的</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>spectacular (壮观震撼的)</t>
+          <t>communication (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1798</v>
+        <v>176</v>
       </c>
       <c r="F11" t="n">
-        <v>4.956</v>
+        <v>4.665</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ANTICIPATION</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -816,31 +816,31 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>spectacular</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>壮观震撼的</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>communication (情绪与感知词汇)</t>
+          <t>spectacular (壮观震撼的)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>176</v>
+        <v>1798</v>
       </c>
       <c r="F12" t="n">
-        <v>4.665</v>
+        <v>4.956</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>ANTICIPATION</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>journey</t>
+          <t>leave</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -860,21 +860,21 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>journey (情绪与感知词汇)</t>
+          <t>leave (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="F13" t="n">
-        <v>4.904</v>
+        <v>4.634</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>SADNESS</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>leave</t>
+          <t>disappointed</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -894,17 +894,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>leave (情绪与感知词汇)</t>
+          <t>disappointed (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>191</v>
+        <v>495</v>
       </c>
       <c r="F14" t="n">
-        <v>4.634</v>
+        <v>4.444</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.05</v>
+        <v>-2.1</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>disappointed</t>
+          <t>journey</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -928,21 +928,21 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>disappointed (情绪与感知词汇)</t>
+          <t>journey (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>495</v>
+        <v>166</v>
       </c>
       <c r="F15" t="n">
-        <v>4.444</v>
+        <v>4.904</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.525</v>
+        <v>0</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>SADNESS</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>0.725</v>
+        <v>2.9</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>flying</t>
+          <t>signature</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -996,21 +996,21 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>flying (情绪与感知词汇)</t>
+          <t>signature (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2740</v>
+        <v>18</v>
       </c>
       <c r="F17" t="n">
-        <v>4.911</v>
+        <v>4.778</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>FEAR</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>signature</t>
+          <t>justice</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1030,17 +1030,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>signature (情绪与感知词汇)</t>
+          <t>justice (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>18</v>
+        <v>114</v>
       </c>
       <c r="F18" t="n">
-        <v>4.778</v>
+        <v>4.982</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1054,31 +1054,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>interesting</t>
+          <t>desert</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>有趣的/引人入胜的</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>interesting (有趣的/引人入胜的)</t>
+          <t>desert (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>859</v>
+        <v>38</v>
       </c>
       <c r="F19" t="n">
-        <v>4.916</v>
+        <v>4.737</v>
       </c>
       <c r="G19" t="n">
-        <v>0.425</v>
+        <v>0</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>CATE</t>
+          <t>SADNESS</t>
         </is>
       </c>
     </row>
@@ -1088,31 +1088,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>desert</t>
+          <t>helpful</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>大有帮助的/热心的</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>desert (情绪与感知词汇)</t>
+          <t>helpful (大有帮助的/热心的)</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>38</v>
+        <v>1115</v>
       </c>
       <c r="F20" t="n">
-        <v>4.737</v>
+        <v>4.948</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>SADNESS</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
         <v>4.962</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1156,31 +1156,31 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>justice</t>
+          <t>interesting</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>有趣的/引人入胜的</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>justice (情绪与感知词汇)</t>
+          <t>interesting (有趣的/引人入胜的)</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>114</v>
+        <v>859</v>
       </c>
       <c r="F22" t="n">
-        <v>4.982</v>
+        <v>4.916</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>CATE</t>
         </is>
       </c>
     </row>
@@ -1190,31 +1190,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>helpful</t>
+          <t>flying</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>大有帮助的/热心的</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>helpful (大有帮助的/热心的)</t>
+          <t>flying (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1115</v>
+        <v>2740</v>
       </c>
       <c r="F23" t="n">
-        <v>4.948</v>
+        <v>4.911</v>
       </c>
       <c r="G23" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>FEAR</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
         <v>4.929</v>
       </c>
       <c r="G25" t="n">
-        <v>0.475</v>
+        <v>1.9</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>4.961</v>
       </c>
       <c r="G26" t="n">
-        <v>0.675</v>
+        <v>2.7</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1326,31 +1326,31 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>patient</t>
+          <t>top</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>耐心周到的</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>patient (耐心周到的)</t>
+          <t>top (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>146</v>
+        <v>1000</v>
       </c>
       <c r="F27" t="n">
-        <v>4.938</v>
+        <v>4.91</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>ANTICIPATION</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -1360,31 +1360,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>skilled</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>操控熟练的/专业的</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>top (情绪与感知词汇)</t>
+          <t>skilled (操控熟练的/专业的)</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="F28" t="n">
-        <v>4.91</v>
+        <v>4.954</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>CATE</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>young</t>
+          <t>smiling</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1404,17 +1404,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>young (情绪与感知词汇)</t>
+          <t>smiling (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>254</v>
+        <v>34</v>
       </c>
       <c r="F29" t="n">
-        <v>4.827</v>
+        <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>smiling</t>
+          <t>kudos</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>smiling (情绪与感知词汇)</t>
+          <t>kudos (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F30" t="n">
         <v>5</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1462,31 +1462,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>skilled</t>
+          <t>young</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>操控熟练的/专业的</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>skilled (操控熟练的/专业的)</t>
+          <t>young (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="F31" t="n">
-        <v>4.954</v>
+        <v>4.827</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>CATE</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>kudos</t>
+          <t>ready</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1506,21 +1506,21 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>kudos (情绪与感知词汇)</t>
+          <t>ready (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>30</v>
+        <v>170</v>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>4.629</v>
       </c>
       <c r="G32" t="n">
-        <v>0.575</v>
+        <v>1.5</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>ANTICIPATION</t>
         </is>
       </c>
     </row>
@@ -1530,31 +1530,31 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>cherish</t>
+          <t>patient</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>耐心周到的</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>cherish (情绪与感知词汇)</t>
+          <t>patient (耐心周到的)</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>54</v>
+        <v>146</v>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>4.938</v>
       </c>
       <c r="G33" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>ANTICIPATION</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ready</t>
+          <t>cherish</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1574,21 +1574,21 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ready (情绪与感知词汇)</t>
+          <t>cherish (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>170</v>
+        <v>54</v>
       </c>
       <c r="F34" t="n">
-        <v>4.629</v>
+        <v>5</v>
       </c>
       <c r="G34" t="n">
-        <v>0.375</v>
+        <v>1.6</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>ANTICIPATION</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
         <v>4.975</v>
       </c>
       <c r="G35" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1666,31 +1666,31 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>experienced</t>
+          <t>terrific</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>经验丰富的</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>experienced (经验丰富的)</t>
+          <t>terrific (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>865</v>
+        <v>278</v>
       </c>
       <c r="F37" t="n">
-        <v>4.94</v>
+        <v>4.964</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>SADNESS</t>
         </is>
       </c>
     </row>
@@ -1700,31 +1700,31 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>terrific</t>
+          <t>experienced</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>经验丰富的</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>terrific (情绪与感知词汇)</t>
+          <t>experienced (经验丰富的)</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>278</v>
+        <v>865</v>
       </c>
       <c r="F38" t="n">
-        <v>4.964</v>
+        <v>4.94</v>
       </c>
       <c r="G38" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>SADNESS</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -1734,31 +1734,31 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>lovely</t>
+          <t>noise</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>噪音/降噪耳机</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>lovely (情绪与感知词汇)</t>
+          <t>noise (噪音/降噪耳机)</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>268</v>
+        <v>166</v>
       </c>
       <c r="F39" t="n">
-        <v>4.899</v>
+        <v>4.873</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>CATE</t>
         </is>
       </c>
     </row>
@@ -1768,31 +1768,31 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>noise</t>
+          <t>lovely</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>噪音/降噪耳机</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>noise (噪音/降噪耳机)</t>
+          <t>lovely (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>166</v>
+        <v>268</v>
       </c>
       <c r="F40" t="n">
-        <v>4.873</v>
+        <v>4.899</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>CATE</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>adventure</t>
+          <t>opportunity</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1846,17 +1846,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>adventure (情绪与感知词汇)</t>
+          <t>opportunity (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1255</v>
+        <v>533</v>
       </c>
       <c r="F42" t="n">
-        <v>4.947</v>
+        <v>4.874</v>
       </c>
       <c r="G42" t="n">
-        <v>0.325</v>
+        <v>1.8</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>4.966</v>
       </c>
       <c r="G43" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>4.957</v>
       </c>
       <c r="G44" t="n">
-        <v>0.625</v>
+        <v>2.5</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>opportunity</t>
+          <t>adventure</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1948,17 +1948,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>opportunity (情绪与感知词汇)</t>
+          <t>adventure (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>533</v>
+        <v>1255</v>
       </c>
       <c r="F45" t="n">
-        <v>4.874</v>
+        <v>4.947</v>
       </c>
       <c r="G45" t="n">
-        <v>0.45</v>
+        <v>1.3</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -1972,31 +1972,31 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>extra</t>
+          <t>friendliness</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>额外的/附加体验</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>extra (额外的/附加体验)</t>
+          <t>friendliness (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>533</v>
+        <v>45</v>
       </c>
       <c r="F46" t="n">
-        <v>4.88</v>
+        <v>4.978</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>CATE</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -2006,31 +2006,31 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>pretty</t>
+          <t>extra</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>额外的/附加体验</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>pretty (情绪与感知词汇)</t>
+          <t>extra (额外的/附加体验)</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>390</v>
+        <v>533</v>
       </c>
       <c r="F47" t="n">
-        <v>4.71</v>
+        <v>4.88</v>
       </c>
       <c r="G47" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>CATE</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>friendliness</t>
+          <t>pretty</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>friendliness (情绪与感知词汇)</t>
+          <t>pretty (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>45</v>
+        <v>390</v>
       </c>
       <c r="F48" t="n">
-        <v>4.978</v>
+        <v>4.71</v>
       </c>
       <c r="G48" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>4.922</v>
       </c>
       <c r="G49" t="n">
-        <v>0.725</v>
+        <v>2.9</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>4.891</v>
       </c>
       <c r="G50" t="n">
-        <v>0.275</v>
+        <v>1.1</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2142,27 +2142,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>outstanding</t>
+          <t>gift</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>卓越杰出的</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>outstanding (卓越杰出的)</t>
+          <t>gift (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>567</v>
+        <v>255</v>
       </c>
       <c r="F51" t="n">
-        <v>4.965</v>
+        <v>4.851</v>
       </c>
       <c r="G51" t="n">
-        <v>0.75</v>
+        <v>1.9</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2176,27 +2176,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>gift</t>
+          <t>outstanding</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>卓越杰出的</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>gift (情绪与感知词汇)</t>
+          <t>outstanding (卓越杰出的)</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>255</v>
+        <v>567</v>
       </c>
       <c r="F52" t="n">
-        <v>4.851</v>
+        <v>4.965</v>
       </c>
       <c r="G52" t="n">
-        <v>0.475</v>
+        <v>3</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>turbulence</t>
+          <t>expectation</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2220,21 +2220,21 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>turbulence (情绪与感知词汇)</t>
+          <t>expectation (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>234</v>
+        <v>27</v>
       </c>
       <c r="F53" t="n">
-        <v>4.88</v>
+        <v>4.63</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>FEAR</t>
+          <t>ANTICIPATION</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>turbulence</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2288,21 +2288,21 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>fall (情绪与感知词汇)</t>
+          <t>turbulence (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>58</v>
+        <v>234</v>
       </c>
       <c r="F55" t="n">
-        <v>4.828</v>
+        <v>4.88</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>SADNESS</t>
+          <t>FEAR</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>expectation</t>
+          <t>fall</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2322,21 +2322,21 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>expectation (情绪与感知词汇)</t>
+          <t>fall (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="F56" t="n">
-        <v>4.63</v>
+        <v>4.828</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>ANTICIPATION</t>
+          <t>SADNESS</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>expert</t>
+          <t>guidance</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2356,14 +2356,14 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>expert (情绪与感知词汇)</t>
+          <t>guidance (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="F57" t="n">
-        <v>4.991</v>
+        <v>5</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>guidance</t>
+          <t>expert</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2390,14 +2390,14 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>guidance (情绪与感知词汇)</t>
+          <t>expert (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="F58" t="n">
-        <v>5</v>
+        <v>4.991</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2434,7 +2434,7 @@
         <v>4.979</v>
       </c>
       <c r="G59" t="n">
-        <v>0.375</v>
+        <v>1.5</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>4.926</v>
       </c>
       <c r="G60" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>4.922</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.275</v>
+        <v>-1.1</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>4.952</v>
       </c>
       <c r="G62" t="n">
-        <v>0.675</v>
+        <v>2.7</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>hit</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2594,21 +2594,21 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>hit (情绪与感知词汇)</t>
+          <t>good (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>70</v>
+        <v>2327</v>
       </c>
       <c r="F64" t="n">
-        <v>4.857</v>
+        <v>4.792</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>ANGER</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>hit</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2628,21 +2628,21 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>good (情绪与感知词汇)</t>
+          <t>hit (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2327</v>
+        <v>70</v>
       </c>
       <c r="F65" t="n">
-        <v>4.792</v>
+        <v>4.857</v>
       </c>
       <c r="G65" t="n">
-        <v>0.475</v>
+        <v>0</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>ANGER</t>
         </is>
       </c>
     </row>
@@ -2652,24 +2652,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>chilly</t>
+          <t>culture</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>文化与历史解说</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>chilly (情绪与感知词汇)</t>
+          <t>culture (文化与历史解说)</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="F66" t="n">
-        <v>4.842</v>
+        <v>5</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2686,24 +2686,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>culture</t>
+          <t>chilly</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>文化与历史解说</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>culture (文化与历史解说)</t>
+          <t>chilly (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="F67" t="n">
-        <v>5</v>
+        <v>4.842</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2720,27 +2720,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>special</t>
+          <t>joy</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>愉悦喜悦</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>special (情绪与感知词汇)</t>
+          <t>joy (愉悦喜悦)</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>596</v>
+        <v>68</v>
       </c>
       <c r="F68" t="n">
-        <v>4.945</v>
+        <v>4.853</v>
       </c>
       <c r="G68" t="n">
-        <v>0.425</v>
+        <v>2.8</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -2754,31 +2754,31 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>joy</t>
+          <t>buck</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>愉悦喜悦</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>joy (愉悦喜悦)</t>
+          <t>buck (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="F69" t="n">
-        <v>4.853</v>
+        <v>4.786</v>
       </c>
       <c r="G69" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>SURPRISE</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>buck</t>
+          <t>wild</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2798,14 +2798,14 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>buck (情绪与感知词汇)</t>
+          <t>wild (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="F70" t="n">
-        <v>4.786</v>
+        <v>4.935</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>wild</t>
+          <t>special</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2832,21 +2832,21 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>wild (情绪与感知词汇)</t>
+          <t>special (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>77</v>
+        <v>596</v>
       </c>
       <c r="F71" t="n">
-        <v>4.935</v>
+        <v>4.945</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>SURPRISE</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>departed</t>
+          <t>gorgeous</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2866,21 +2866,21 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>departed (情绪与感知词汇)</t>
+          <t>gorgeous (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>35</v>
+        <v>447</v>
       </c>
       <c r="F72" t="n">
-        <v>4.657</v>
+        <v>4.928</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>SADNESS</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>avoid</t>
+          <t>picnic</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2900,21 +2900,21 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>avoid (情绪与感知词汇)</t>
+          <t>picnic (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="F73" t="n">
-        <v>4.383</v>
+        <v>4.667</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>FEAR</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>arrival</t>
+          <t>kind</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2934,21 +2934,21 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>arrival (情绪与感知词汇)</t>
+          <t>kind (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>158</v>
+        <v>589</v>
       </c>
       <c r="F74" t="n">
-        <v>4.741</v>
+        <v>4.844</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>ANTICIPATION</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>gorgeous</t>
+          <t>arrival</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2968,21 +2968,21 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>gorgeous (情绪与感知词汇)</t>
+          <t>arrival (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>447</v>
+        <v>158</v>
       </c>
       <c r="F75" t="n">
-        <v>4.928</v>
+        <v>4.741</v>
       </c>
       <c r="G75" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>ANTICIPATION</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>kind</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3002,21 +3002,21 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>kind (情绪与感知词汇)</t>
+          <t>long (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="F76" t="n">
-        <v>4.844</v>
+        <v>4.775</v>
       </c>
       <c r="G76" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>ANTICIPATION</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>competent</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3036,21 +3036,21 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>long (情绪与感知词汇)</t>
+          <t>competent (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>583</v>
+        <v>165</v>
       </c>
       <c r="F77" t="n">
-        <v>4.775</v>
+        <v>4.939</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>ANTICIPATION</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>picnic</t>
+          <t>avoid</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3104,21 +3104,21 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>picnic (情绪与感知词汇)</t>
+          <t>avoid (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="F79" t="n">
-        <v>4.667</v>
+        <v>4.383</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>FEAR</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>competent</t>
+          <t>departed</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3138,21 +3138,21 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>competent (情绪与感知词汇)</t>
+          <t>departed (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>165</v>
+        <v>35</v>
       </c>
       <c r="F80" t="n">
-        <v>4.939</v>
+        <v>4.657</v>
       </c>
       <c r="G80" t="n">
-        <v>0.325</v>
+        <v>0</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>SADNESS</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
         <v>4.901</v>
       </c>
       <c r="G81" t="n">
-        <v>0.325</v>
+        <v>1.3</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3196,31 +3196,31 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>enjoy</t>
+          <t>terrible</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>可怕的/极度不满的</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>enjoy (情绪与感知词汇)</t>
+          <t>terrible (可怕的/极度不满的)</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>560</v>
+        <v>50</v>
       </c>
       <c r="F82" t="n">
-        <v>4.85</v>
+        <v>3.16</v>
       </c>
       <c r="G82" t="n">
-        <v>0.55</v>
+        <v>-2.1</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>SADNESS</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>related</t>
+          <t>assured</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3240,17 +3240,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>related (情绪与感知词汇)</t>
+          <t>assured (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="F83" t="n">
-        <v>4.905</v>
+        <v>4.571</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3264,31 +3264,31 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>恐惧/对飞行的害怕</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>fear (恐惧/对飞行的害怕)</t>
+          <t>happy (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>118</v>
+        <v>534</v>
       </c>
       <c r="F84" t="n">
-        <v>4.958</v>
+        <v>4.882</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.55</v>
+        <v>2.7</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>FEAR</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>gate</t>
+          <t>found</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3308,21 +3308,21 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>gate (情绪与感知词汇)</t>
+          <t>found (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>192</v>
+        <v>465</v>
       </c>
       <c r="F85" t="n">
-        <v>4.87</v>
+        <v>4.83</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -3332,31 +3332,31 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>soothing</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>平静镇定的/从容的</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>calm (平静镇定的/从容的)</t>
+          <t>soothing (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>252</v>
+        <v>18</v>
       </c>
       <c r="F86" t="n">
-        <v>4.952</v>
+        <v>4.889</v>
       </c>
       <c r="G86" t="n">
-        <v>0.325</v>
+        <v>1.3</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>CATE</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>found</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3376,21 +3376,21 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>found (情绪与感知词汇)</t>
+          <t>impossible (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>465</v>
+        <v>66</v>
       </c>
       <c r="F87" t="n">
-        <v>4.83</v>
+        <v>4.485</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>SADNESS</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>row</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3410,21 +3410,21 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>impossible (情绪与感知词汇)</t>
+          <t>row (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="F88" t="n">
-        <v>4.485</v>
+        <v>4.579</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>SADNESS</t>
+          <t>ANGER</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>thankful</t>
+          <t>feeling</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3444,17 +3444,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>thankful (情绪与感知词汇)</t>
+          <t>feeling (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>60</v>
+        <v>209</v>
       </c>
       <c r="F89" t="n">
-        <v>4.983</v>
+        <v>4.813</v>
       </c>
       <c r="G89" t="n">
-        <v>0.675</v>
+        <v>0.5</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>thankful</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3478,17 +3478,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>happy (情绪与感知词汇)</t>
+          <t>thankful (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>534</v>
+        <v>60</v>
       </c>
       <c r="F90" t="n">
-        <v>4.882</v>
+        <v>4.983</v>
       </c>
       <c r="G90" t="n">
-        <v>0.675</v>
+        <v>2.7</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>soothing</t>
+          <t>related</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3512,21 +3512,21 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>soothing (情绪与感知词汇)</t>
+          <t>related (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F91" t="n">
-        <v>4.889</v>
+        <v>4.905</v>
       </c>
       <c r="G91" t="n">
-        <v>0.325</v>
+        <v>0</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -3536,31 +3536,31 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>terrible</t>
+          <t>kindness</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>可怕的/极度不满的</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>terrible (可怕的/极度不满的)</t>
+          <t>kindness (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F92" t="n">
-        <v>3.16</v>
+        <v>4.892</v>
       </c>
       <c r="G92" t="n">
-        <v>-0.525</v>
+        <v>2</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>SADNESS</t>
+          <t>CATE</t>
         </is>
       </c>
     </row>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>assured</t>
+          <t>arrive</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3580,21 +3580,21 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>assured (情绪与感知词汇)</t>
+          <t>arrive (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="F93" t="n">
-        <v>4.571</v>
+        <v>4.489</v>
       </c>
       <c r="G93" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>ANTICIPATION</t>
         </is>
       </c>
     </row>
@@ -3604,31 +3604,31 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>expertise</t>
+          <t>calm</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>平静镇定的/从容的</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>expertise (情绪与感知词汇)</t>
+          <t>calm (平静镇定的/从容的)</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>62</v>
+        <v>252</v>
       </c>
       <c r="F94" t="n">
-        <v>4.968</v>
+        <v>4.952</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>CATE</t>
         </is>
       </c>
     </row>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>kindness</t>
+          <t>gate</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3648,21 +3648,21 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>kindness (情绪与感知词汇)</t>
+          <t>gate (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>37</v>
+        <v>192</v>
       </c>
       <c r="F95" t="n">
-        <v>4.892</v>
+        <v>4.87</v>
       </c>
       <c r="G95" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>CATE</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -3672,31 +3672,31 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>row</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>恐惧/对飞行的害怕</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>row (情绪与感知词汇)</t>
+          <t>fear (恐惧/对飞行的害怕)</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F96" t="n">
-        <v>4.579</v>
+        <v>4.958</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>-2.2</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>ANGER</t>
+          <t>FEAR</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>feeling</t>
+          <t>expertise</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3716,21 +3716,21 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>feeling (情绪与感知词汇)</t>
+          <t>expertise (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>209</v>
+        <v>62</v>
       </c>
       <c r="F97" t="n">
-        <v>4.813</v>
+        <v>4.968</v>
       </c>
       <c r="G97" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>arrive</t>
+          <t>enjoy</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3750,21 +3750,21 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>arrive (情绪与感知词汇)</t>
+          <t>enjoy (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>92</v>
+        <v>560</v>
       </c>
       <c r="F98" t="n">
-        <v>4.489</v>
+        <v>4.85</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>ANTICIPATION</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -3774,31 +3774,31 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>priceless</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>无价的/珍贵的</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>priceless (无价的/珍贵的)</t>
+          <t>unique (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>85</v>
+        <v>459</v>
       </c>
       <c r="F99" t="n">
-        <v>5</v>
+        <v>4.948</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>CATE</t>
+          <t>SURPRISE</t>
         </is>
       </c>
     </row>
@@ -3808,31 +3808,31 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>priceless</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>无价的/珍贵的</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>unique (情绪与感知词汇)</t>
+          <t>priceless (无价的/珍贵的)</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>459</v>
+        <v>85</v>
       </c>
       <c r="F100" t="n">
-        <v>4.948</v>
+        <v>5</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>SURPRISE</t>
+          <t>CATE</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
         <v>4.973</v>
       </c>
       <c r="G101" t="n">
-        <v>0.55</v>
+        <v>2.2</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>4.561</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.225</v>
+        <v>-0.9</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>4.75</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.45</v>
+        <v>-1.8</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>4.947</v>
       </c>
       <c r="G108" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>4.41</v>
       </c>
       <c r="G109" t="n">
-        <v>-0.425</v>
+        <v>-1.7</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -4250,27 +4250,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>bad</t>
+          <t>late</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>差劲的</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>bad (差劲的)</t>
+          <t>late (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>356</v>
+        <v>267</v>
       </c>
       <c r="F113" t="n">
-        <v>4.379</v>
+        <v>4.449</v>
       </c>
       <c r="G113" t="n">
-        <v>-0.625</v>
+        <v>0</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -4284,27 +4284,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>late</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>差劲的</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>late (情绪与感知词汇)</t>
+          <t>bad (差劲的)</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>267</v>
+        <v>356</v>
       </c>
       <c r="F114" t="n">
-        <v>4.449</v>
+        <v>4.379</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>honest</t>
+          <t>law</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4328,21 +4328,21 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>honest (情绪与感知词汇)</t>
+          <t>law (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="F115" t="n">
-        <v>4.581</v>
+        <v>4.83</v>
       </c>
       <c r="G115" t="n">
-        <v>0.575</v>
+        <v>0</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>hate</t>
+          <t>risk</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4362,21 +4362,21 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>hate (情绪与感知词汇)</t>
+          <t>risk (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F116" t="n">
-        <v>4.607</v>
+        <v>4.5</v>
       </c>
       <c r="G116" t="n">
-        <v>-0.675</v>
+        <v>-1.1</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>SADNESS</t>
+          <t>ANTICIPATION</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>possibility</t>
+          <t>honest</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4396,21 +4396,21 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>possibility (情绪与感知词汇)</t>
+          <t>honest (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="F117" t="n">
-        <v>4.325</v>
+        <v>4.581</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>ANTICIPATION</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>surprised</t>
+          <t>possibility</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4430,21 +4430,21 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>surprised (情绪与感知词汇)</t>
+          <t>possibility (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>196</v>
+        <v>40</v>
       </c>
       <c r="F118" t="n">
-        <v>4.862</v>
+        <v>4.325</v>
       </c>
       <c r="G118" t="n">
-        <v>0.225</v>
+        <v>0</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>SURPRISE</t>
+          <t>ANTICIPATION</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>county</t>
+          <t>hate</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4464,21 +4464,21 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>county (情绪与感知词汇)</t>
+          <t>hate (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="F119" t="n">
-        <v>4.909</v>
+        <v>4.607</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>-2.7</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>SADNESS</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>law</t>
+          <t>county</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4498,14 +4498,14 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>law (情绪与感知词汇)</t>
+          <t>county (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F120" t="n">
-        <v>4.83</v>
+        <v>4.909</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -4522,31 +4522,31 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>provide</t>
+          <t>awful</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>极糟糕的</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>provide (情绪与感知词汇)</t>
+          <t>awful (极糟糕的)</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>242</v>
+        <v>15</v>
       </c>
       <c r="F121" t="n">
-        <v>4.723</v>
+        <v>2.2</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>SADNESS</t>
         </is>
       </c>
     </row>
@@ -4556,31 +4556,31 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>awful</t>
+          <t>surprised</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>极糟糕的</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>awful (极糟糕的)</t>
+          <t>surprised (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>15</v>
+        <v>196</v>
       </c>
       <c r="F122" t="n">
-        <v>2.2</v>
+        <v>4.862</v>
       </c>
       <c r="G122" t="n">
-        <v>-0.5</v>
+        <v>0.9</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>SADNESS</t>
+          <t>SURPRISE</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>risk</t>
+          <t>provide</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4600,21 +4600,21 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>risk (情绪与感知词汇)</t>
+          <t>provide (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>38</v>
+        <v>242</v>
       </c>
       <c r="F123" t="n">
-        <v>4.5</v>
+        <v>4.723</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.275</v>
+        <v>0</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>ANTICIPATION</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
         <v>4.922</v>
       </c>
       <c r="G126" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>4.957</v>
       </c>
       <c r="G127" t="n">
-        <v>0.475</v>
+        <v>1.9</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -4794,31 +4794,31 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>blast</t>
+          <t>personable</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>平易近人的/亲切的</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>blast (情绪与感知词汇)</t>
+          <t>personable (平易近人的/亲切的)</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>185</v>
+        <v>418</v>
       </c>
       <c r="F129" t="n">
-        <v>4.968</v>
+        <v>4.969</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>SURPRISE</t>
+          <t>CATE</t>
         </is>
       </c>
     </row>
@@ -4862,31 +4862,31 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>personable</t>
+          <t>blast</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>平易近人的/亲切的</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>personable (平易近人的/亲切的)</t>
+          <t>blast (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>418</v>
+        <v>185</v>
       </c>
       <c r="F131" t="n">
-        <v>4.969</v>
+        <v>4.968</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>CATE</t>
+          <t>SURPRISE</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>hurry</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4940,21 +4940,21 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>hurry (情绪与感知词汇)</t>
+          <t>base (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="F133" t="n">
-        <v>3.867</v>
+        <v>4.88</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>ANTICIPATION</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -4964,7 +4964,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>hurry</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4974,21 +4974,21 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>base (情绪与感知词汇)</t>
+          <t>hurry (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>368</v>
+        <v>15</v>
       </c>
       <c r="F134" t="n">
-        <v>4.88</v>
+        <v>3.867</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>ANTICIPATION</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
         <v>4.899</v>
       </c>
       <c r="G135" t="n">
-        <v>0.425</v>
+        <v>1.7</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>4.741</v>
       </c>
       <c r="G137" t="n">
-        <v>0.475</v>
+        <v>1.9</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>5</v>
       </c>
       <c r="G139" t="n">
-        <v>-0.65</v>
+        <v>-2.6</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>passenger</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5178,21 +5178,21 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>passenger (情绪与感知词汇)</t>
+          <t>friend (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>353</v>
+        <v>241</v>
       </c>
       <c r="F140" t="n">
-        <v>4.824</v>
+        <v>4.938</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>ANTICIPATION</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>friend</t>
+          <t>worry</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5212,21 +5212,21 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>friend (情绪与感知词汇)</t>
+          <t>worry (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>241</v>
+        <v>105</v>
       </c>
       <c r="F141" t="n">
-        <v>4.938</v>
+        <v>4.943</v>
       </c>
       <c r="G141" t="n">
-        <v>0.55</v>
+        <v>-1.9</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>SADNESS</t>
         </is>
       </c>
     </row>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>worry</t>
+          <t>passenger</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5246,21 +5246,21 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>worry (情绪与感知词汇)</t>
+          <t>passenger (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>105</v>
+        <v>353</v>
       </c>
       <c r="F142" t="n">
-        <v>4.943</v>
+        <v>4.824</v>
       </c>
       <c r="G142" t="n">
-        <v>-0.475</v>
+        <v>0</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>SADNESS</t>
+          <t>ANTICIPATION</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
         <v>4.945</v>
       </c>
       <c r="G143" t="n">
-        <v>0.55</v>
+        <v>2.2</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>highest</t>
+          <t>expect</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5314,21 +5314,21 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>highest (情绪与感知词汇)</t>
+          <t>expect (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>81</v>
+        <v>204</v>
       </c>
       <c r="F144" t="n">
-        <v>4.889</v>
+        <v>4.77</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>expect</t>
+          <t>expected</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5348,21 +5348,21 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>expect (情绪与感知词汇)</t>
+          <t>expected (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>204</v>
+        <v>282</v>
       </c>
       <c r="F145" t="n">
-        <v>4.77</v>
+        <v>4.752</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>ANTICIPATION</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5392,7 @@
         <v>4.446</v>
       </c>
       <c r="G146" t="n">
-        <v>-0.225</v>
+        <v>-0.9</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>expected</t>
+          <t>highest</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5416,21 +5416,21 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>expected (情绪与感知词汇)</t>
+          <t>highest (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>282</v>
+        <v>81</v>
       </c>
       <c r="F147" t="n">
-        <v>4.752</v>
+        <v>4.889</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>ANTICIPATION</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -5440,31 +5440,31 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>gem</t>
+          <t>cold</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>高空微凉/客舱气温</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>gem (情绪与感知词汇)</t>
+          <t>cold (高空微凉/客舱气温)</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>23</v>
+        <v>170</v>
       </c>
       <c r="F148" t="n">
-        <v>4.957</v>
+        <v>4.847</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>CATE</t>
         </is>
       </c>
     </row>
@@ -5474,31 +5474,31 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>cold</t>
+          <t>gem</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>高空微凉/客舱气温</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>cold (高空微凉/客舱气温)</t>
+          <t>gem (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>170</v>
+        <v>23</v>
       </c>
       <c r="F149" t="n">
-        <v>4.847</v>
+        <v>4.957</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>CATE</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -5508,31 +5508,31 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>major</t>
+          <t>sweet</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>核心亮点/主要看点</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>major (核心亮点/主要看点)</t>
+          <t>sweet (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="F150" t="n">
-        <v>4.85</v>
+        <v>4.919</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>CATE</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>fearful</t>
+          <t>sick</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5552,17 +5552,17 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>fearful (情绪与感知词汇)</t>
+          <t>sick (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>22</v>
+        <v>240</v>
       </c>
       <c r="F151" t="n">
-        <v>4.818</v>
+        <v>4.758</v>
       </c>
       <c r="G151" t="n">
-        <v>-0.55</v>
+        <v>-2.3</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -5576,31 +5576,31 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>sick</t>
+          <t>major</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>核心亮点/主要看点</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>sick (情绪与感知词汇)</t>
+          <t>major (核心亮点/主要看点)</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="F152" t="n">
-        <v>4.758</v>
+        <v>4.85</v>
       </c>
       <c r="G152" t="n">
-        <v>-0.575</v>
+        <v>0</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>SADNESS</t>
+          <t>CATE</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>sweet</t>
+          <t>fearful</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5620,21 +5620,21 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>sweet (情绪与感知词汇)</t>
+          <t>fearful (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="F153" t="n">
-        <v>4.919</v>
+        <v>4.818</v>
       </c>
       <c r="G153" t="n">
-        <v>0.5</v>
+        <v>-2.2</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>SADNESS</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
         <v>3.983</v>
       </c>
       <c r="G154" t="n">
-        <v>-0.325</v>
+        <v>-1.3</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>older</t>
+          <t>hearing</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5790,21 +5790,21 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>older (情绪与感知词汇)</t>
+          <t>hearing (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F158" t="n">
-        <v>4.766</v>
+        <v>4.759</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>SADNESS</t>
+          <t>FEAR</t>
         </is>
       </c>
     </row>
@@ -5814,27 +5814,27 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>surprise</t>
+          <t>treat</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>惊喜惊奇</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>surprise (惊喜惊奇)</t>
+          <t>treat (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="F159" t="n">
-        <v>4.867</v>
+        <v>4.878</v>
       </c>
       <c r="G159" t="n">
-        <v>0.275</v>
+        <v>1.7</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>hearing</t>
+          <t>older</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5858,21 +5858,21 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>hearing (情绪与感知词汇)</t>
+          <t>older (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F160" t="n">
-        <v>4.759</v>
+        <v>4.766</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>FEAR</t>
+          <t>SADNESS</t>
         </is>
       </c>
     </row>
@@ -5882,27 +5882,27 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>treat</t>
+          <t>surprise</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>惊喜惊奇</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>treat (情绪与感知词汇)</t>
+          <t>surprise (惊喜惊奇)</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F161" t="n">
-        <v>4.878</v>
+        <v>4.867</v>
       </c>
       <c r="G161" t="n">
-        <v>0.425</v>
+        <v>1.1</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         <v>4.903</v>
       </c>
       <c r="G163" t="n">
-        <v>0.45</v>
+        <v>1.8</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
         <v>4.947</v>
       </c>
       <c r="G164" t="n">
-        <v>0.775</v>
+        <v>3.1</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>treasure</t>
+          <t>pleased</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6028,17 +6028,17 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>treasure (情绪与感知词汇)</t>
+          <t>pleased (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="F165" t="n">
-        <v>5</v>
+        <v>4.924</v>
       </c>
       <c r="G165" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>pleased</t>
+          <t>treasure</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6062,17 +6062,17 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>pleased (情绪与感知词汇)</t>
+          <t>treasure (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>132</v>
+        <v>54</v>
       </c>
       <c r="F166" t="n">
-        <v>4.924</v>
+        <v>5</v>
       </c>
       <c r="G166" t="n">
-        <v>0.475</v>
+        <v>1.2</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -6086,31 +6086,31 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>completely</t>
+          <t>constant</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>完全地/彻底地</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>completely (完全地/彻底地)</t>
+          <t>constant (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>326</v>
+        <v>41</v>
       </c>
       <c r="F167" t="n">
-        <v>4.752</v>
+        <v>4.512</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>CATE</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>unsafe</t>
+          <t>majority</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6130,21 +6130,21 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>unsafe (情绪与感知词汇)</t>
+          <t>majority (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F168" t="n">
-        <v>4.657</v>
+        <v>4.323</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>FEAR</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6164,14 +6164,14 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>fixed (情绪与感知词汇)</t>
+          <t>confirmed (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="F169" t="n">
-        <v>4.847</v>
+        <v>3.971</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ill</t>
+          <t>turbulent</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6198,21 +6198,21 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>ill (情绪与感知词汇)</t>
+          <t>turbulent (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F170" t="n">
-        <v>4.217</v>
+        <v>4.645</v>
       </c>
       <c r="G170" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>SADNESS</t>
+          <t>FEAR</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>turbulent</t>
+          <t>fixed</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6232,21 +6232,21 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>turbulent (情绪与感知词汇)</t>
+          <t>fixed (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>31</v>
+        <v>196</v>
       </c>
       <c r="F171" t="n">
-        <v>4.645</v>
+        <v>4.847</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>FEAR</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -6256,31 +6256,31 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>majority</t>
+          <t>worse</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>更糟糕的</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>majority (情绪与感知词汇)</t>
+          <t>worse (更糟糕的)</t>
         </is>
       </c>
       <c r="E172" t="n">
         <v>31</v>
       </c>
       <c r="F172" t="n">
-        <v>4.323</v>
+        <v>3.71</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>-2.1</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>SADNESS</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>ill</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6300,21 +6300,21 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>confirmed (情绪与感知词汇)</t>
+          <t>ill (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F173" t="n">
-        <v>3.971</v>
+        <v>4.217</v>
       </c>
       <c r="G173" t="n">
-        <v>0</v>
+        <v>-1.8</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>SADNESS</t>
         </is>
       </c>
     </row>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>unable</t>
+          <t>finally</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6334,21 +6334,21 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>unable (情绪与感知词汇)</t>
+          <t>finally (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>112</v>
+        <v>210</v>
       </c>
       <c r="F174" t="n">
-        <v>4.464</v>
+        <v>4.471</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>SADNESS</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>skeptical</t>
+          <t>unsafe</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6368,21 +6368,21 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>skeptical (情绪与感知词汇)</t>
+          <t>unsafe (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F175" t="n">
-        <v>4.818</v>
+        <v>4.657</v>
       </c>
       <c r="G175" t="n">
-        <v>-0.325</v>
+        <v>0</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>CATE</t>
+          <t>FEAR</t>
         </is>
       </c>
     </row>
@@ -6392,27 +6392,27 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>disappointing</t>
+          <t>unable</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>令人失望的</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>disappointing (令人失望的)</t>
+          <t>unable (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="F176" t="n">
-        <v>2.813</v>
+        <v>4.464</v>
       </c>
       <c r="G176" t="n">
-        <v>-0.55</v>
+        <v>0</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -6426,31 +6426,31 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>worse</t>
+          <t>shoulder</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>更糟糕的</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>worse (更糟糕的)</t>
+          <t>shoulder (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F177" t="n">
-        <v>3.71</v>
+        <v>4.562</v>
       </c>
       <c r="G177" t="n">
-        <v>-0.525</v>
+        <v>0</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>SADNESS</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -6460,31 +6460,31 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>shoulder</t>
+          <t>disappointing</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>令人失望的</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>shoulder (情绪与感知词汇)</t>
+          <t>disappointing (令人失望的)</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F178" t="n">
-        <v>4.562</v>
+        <v>2.813</v>
       </c>
       <c r="G178" t="n">
-        <v>0</v>
+        <v>-2.2</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>SADNESS</t>
         </is>
       </c>
     </row>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>finally</t>
+          <t>skeptical</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6504,21 +6504,21 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>finally (情绪与感知词汇)</t>
+          <t>skeptical (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>210</v>
+        <v>22</v>
       </c>
       <c r="F179" t="n">
-        <v>4.471</v>
+        <v>4.818</v>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>CATE</t>
         </is>
       </c>
     </row>
@@ -6528,31 +6528,31 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>constant</t>
+          <t>completely</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>完全地/彻底地</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>constant (情绪与感知词汇)</t>
+          <t>completely (完全地/彻底地)</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>41</v>
+        <v>326</v>
       </c>
       <c r="F180" t="n">
-        <v>4.512</v>
+        <v>4.752</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>CATE</t>
         </is>
       </c>
     </row>
@@ -6562,31 +6562,31 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>effort</t>
+          <t>improve</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>用心安排/商家付出</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>effort (用心安排/商家付出)</t>
+          <t>improve (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="F181" t="n">
-        <v>4.694</v>
+        <v>4.412</v>
       </c>
       <c r="G181" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>CATE</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -6596,31 +6596,31 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>sunset</t>
+          <t>effort</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>用心安排/商家付出</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>sunset (情绪与感知词汇)</t>
+          <t>effort (用心安排/商家付出)</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>268</v>
+        <v>85</v>
       </c>
       <c r="F182" t="n">
-        <v>4.873</v>
+        <v>4.694</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>ANTICIPATION</t>
+          <t>CATE</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>board</t>
+          <t>fill</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6640,21 +6640,21 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>board (情绪与感知词汇)</t>
+          <t>fill (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>218</v>
+        <v>39</v>
       </c>
       <c r="F183" t="n">
-        <v>4.725</v>
+        <v>4.462</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>ANTICIPATION</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -6664,7 +6664,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>fill</t>
+          <t>sunset</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6674,21 +6674,21 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>fill (情绪与感知词汇)</t>
+          <t>sunset (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>39</v>
+        <v>268</v>
       </c>
       <c r="F184" t="n">
-        <v>4.462</v>
+        <v>4.873</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>ANTICIPATION</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>improve</t>
+          <t>board</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6708,21 +6708,21 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>improve (情绪与感知词汇)</t>
+          <t>board (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>17</v>
+        <v>218</v>
       </c>
       <c r="F185" t="n">
-        <v>4.412</v>
+        <v>4.725</v>
       </c>
       <c r="G185" t="n">
-        <v>0.475</v>
+        <v>0</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>ANTICIPATION</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6820,7 @@
         <v>4.724</v>
       </c>
       <c r="G188" t="n">
-        <v>0.125</v>
+        <v>0.5</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         <v>4.951</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.45</v>
+        <v>-1.8</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -6868,31 +6868,31 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>wasted</t>
+          <t>beach</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>浪钱浪费时间的</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>wasted (浪钱浪费时间的)</t>
+          <t>beach (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>33</v>
+        <v>219</v>
       </c>
       <c r="F190" t="n">
-        <v>2.455</v>
+        <v>4.877</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.55</v>
+        <v>0</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>DISGUST</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -6902,31 +6902,31 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>beach</t>
+          <t>wasted</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>浪钱浪费时间的</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>beach (情绪与感知词汇)</t>
+          <t>wasted (浪钱浪费时间的)</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>219</v>
+        <v>33</v>
       </c>
       <c r="F191" t="n">
-        <v>4.877</v>
+        <v>2.455</v>
       </c>
       <c r="G191" t="n">
-        <v>0</v>
+        <v>-2.2</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>DISGUST</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
         <v>4.56</v>
       </c>
       <c r="G192" t="n">
-        <v>-0.525</v>
+        <v>-2.1</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>advise</t>
+          <t>pleasant</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6980,21 +6980,21 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>advise (情绪与感知词汇)</t>
+          <t>pleasant (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>47</v>
+        <v>299</v>
       </c>
       <c r="F193" t="n">
-        <v>4.66</v>
+        <v>4.876</v>
       </c>
       <c r="G193" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>pleasant</t>
+          <t>advise</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7014,21 +7014,21 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>pleasant (情绪与感知词汇)</t>
+          <t>advise (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>299</v>
+        <v>47</v>
       </c>
       <c r="F194" t="n">
-        <v>4.876</v>
+        <v>4.66</v>
       </c>
       <c r="G194" t="n">
-        <v>0.575</v>
+        <v>0</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>excited</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7048,21 +7048,21 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>excited (情绪与感知词汇)</t>
+          <t>stable (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>162</v>
+        <v>76</v>
       </c>
       <c r="F195" t="n">
-        <v>4.753</v>
+        <v>4.882</v>
       </c>
       <c r="G195" t="n">
-        <v>0.35</v>
+        <v>1.2</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -7072,31 +7072,31 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>uncomfortable</t>
+          <t>fact</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>身体不适/颠簸反感</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>uncomfortable (身体不适/颠簸反感)</t>
+          <t>fact (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>55</v>
+        <v>203</v>
       </c>
       <c r="F196" t="n">
-        <v>3.982</v>
+        <v>4.675</v>
       </c>
       <c r="G196" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>CATE</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7116,21 +7116,21 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>stable (情绪与感知词汇)</t>
+          <t>hot (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="F197" t="n">
-        <v>4.882</v>
+        <v>4.557</v>
       </c>
       <c r="G197" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>ANGER</t>
         </is>
       </c>
     </row>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>hot</t>
+          <t>excited</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7150,21 +7150,21 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>hot (情绪与感知词汇)</t>
+          <t>excited (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>106</v>
+        <v>162</v>
       </c>
       <c r="F198" t="n">
-        <v>4.557</v>
+        <v>4.753</v>
       </c>
       <c r="G198" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>ANGER</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -7174,31 +7174,31 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>fact</t>
+          <t>uncomfortable</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>身体不适/颠簸反感</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>fact (情绪与感知词汇)</t>
+          <t>uncomfortable (身体不适/颠簸反感)</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>203</v>
+        <v>55</v>
       </c>
       <c r="F199" t="n">
-        <v>4.675</v>
+        <v>3.982</v>
       </c>
       <c r="G199" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>CATE</t>
         </is>
       </c>
     </row>
@@ -7242,7 +7242,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>watch</t>
+          <t>eagle</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7252,21 +7252,21 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>watch (情绪与感知词汇)</t>
+          <t>eagle (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>121</v>
+        <v>59</v>
       </c>
       <c r="F201" t="n">
-        <v>4.843</v>
+        <v>4.847</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>ANTICIPATION</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>eagle</t>
+          <t>watch</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7286,21 +7286,21 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>eagle (情绪与感知词汇)</t>
+          <t>watch (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>59</v>
+        <v>121</v>
       </c>
       <c r="F202" t="n">
-        <v>4.847</v>
+        <v>4.843</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>ANTICIPATION</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>nausea</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7320,21 +7320,21 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>warning (情绪与感知词汇)</t>
+          <t>nausea (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F203" t="n">
-        <v>4.293</v>
+        <v>4.735</v>
       </c>
       <c r="G203" t="n">
-        <v>-0.35</v>
+        <v>0</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>FEAR</t>
+          <t>DISGUST</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>nausea</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7354,21 +7354,21 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>nausea (情绪与感知词汇)</t>
+          <t>warning (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="F204" t="n">
-        <v>4.735</v>
+        <v>4.293</v>
       </c>
       <c r="G204" t="n">
-        <v>0</v>
+        <v>-1.4</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>DISGUST</t>
+          <t>FEAR</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
         <v>5</v>
       </c>
       <c r="G205" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>4.692</v>
       </c>
       <c r="G206" t="n">
-        <v>0.425</v>
+        <v>1.7</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>4.545</v>
       </c>
       <c r="G211" t="n">
-        <v>0.325</v>
+        <v>1.3</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>4.886</v>
       </c>
       <c r="G213" t="n">
-        <v>0.45</v>
+        <v>1.8</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>4.5</v>
       </c>
       <c r="G214" t="n">
-        <v>-0.375</v>
+        <v>-1.5</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>4.937</v>
       </c>
       <c r="G217" t="n">
-        <v>-0.425</v>
+        <v>-1.7</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>familiar</t>
+          <t>communicative</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -7830,21 +7830,21 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>familiar (情绪与感知词汇)</t>
+          <t>communicative (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="F218" t="n">
-        <v>4.857</v>
+        <v>5</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>CATE</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>communicative</t>
+          <t>familiar</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -7864,21 +7864,21 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>communicative (情绪与感知词汇)</t>
+          <t>familiar (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="F219" t="n">
-        <v>5</v>
+        <v>4.857</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>CATE</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -7908,7 +7908,7 @@
         <v>5</v>
       </c>
       <c r="G220" t="n">
-        <v>0.425</v>
+        <v>1.7</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>4.473</v>
       </c>
       <c r="G221" t="n">
-        <v>-0.675</v>
+        <v>-2.7</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>4.935</v>
       </c>
       <c r="G222" t="n">
-        <v>-0.375</v>
+        <v>-1.5</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>3.848</v>
       </c>
       <c r="G223" t="n">
-        <v>-0.325</v>
+        <v>-1.3</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         <v>4.938</v>
       </c>
       <c r="G224" t="n">
-        <v>0.55</v>
+        <v>2.2</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>4.885</v>
       </c>
       <c r="G230" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>4.882</v>
       </c>
       <c r="G231" t="n">
-        <v>0.625</v>
+        <v>2.5</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -8296,31 +8296,31 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>cooperating</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>取消行程/退订的</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>cooperating (情绪与感知词汇)</t>
+          <t>cancel (取消行程/退订的)</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>34</v>
+        <v>131</v>
       </c>
       <c r="F232" t="n">
-        <v>4.853</v>
+        <v>4.634</v>
       </c>
       <c r="G232" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>SADNESS</t>
         </is>
       </c>
     </row>
@@ -8330,31 +8330,31 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>cooperating</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>取消行程/退订的</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>cancel (取消行程/退订的)</t>
+          <t>cooperating (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>131</v>
+        <v>34</v>
       </c>
       <c r="F233" t="n">
-        <v>4.634</v>
+        <v>4.853</v>
       </c>
       <c r="G233" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>SADNESS</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -8364,31 +8364,31 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>rainy</t>
+          <t>grateful</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>感激的/感恩的</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>rainy (情绪与感知词汇)</t>
+          <t>grateful (感激的/感恩的)</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="F234" t="n">
-        <v>4.779</v>
+        <v>4.926</v>
       </c>
       <c r="G234" t="n">
-        <v>-0.075</v>
+        <v>2</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>SADNESS</t>
+          <t>CATE</t>
         </is>
       </c>
     </row>
@@ -8398,31 +8398,31 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>grateful</t>
+          <t>rainy</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>感激的/感恩的</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>grateful (感激的/感恩的)</t>
+          <t>rainy (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="F235" t="n">
-        <v>4.926</v>
+        <v>4.779</v>
       </c>
       <c r="G235" t="n">
-        <v>0.5</v>
+        <v>-0.3</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>CATE</t>
+          <t>SADNESS</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>delicious</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8442,21 +8442,21 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>delicious (情绪与感知词汇)</t>
+          <t>black (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="F236" t="n">
-        <v>5</v>
+        <v>4.921</v>
       </c>
       <c r="G236" t="n">
-        <v>0.675</v>
+        <v>0</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>SADNESS</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>black</t>
+          <t>bear</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8476,21 +8476,21 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>black (情绪与感知词汇)</t>
+          <t>bear (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>76</v>
+        <v>214</v>
       </c>
       <c r="F237" t="n">
-        <v>4.921</v>
+        <v>4.879</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>SADNESS</t>
+          <t>FEAR</t>
         </is>
       </c>
     </row>
@@ -8500,31 +8500,31 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>unbelievable</t>
+          <t>delicious</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>难以置信的/超乎想象的</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>unbelievable (难以置信的/超乎想象的)</t>
+          <t>delicious (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>348</v>
+        <v>35</v>
       </c>
       <c r="F238" t="n">
-        <v>4.983</v>
+        <v>5</v>
       </c>
       <c r="G238" t="n">
-        <v>0.2</v>
+        <v>2.7</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>CATE</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -8534,31 +8534,31 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>bear</t>
+          <t>unbelievable</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>难以置信的/超乎想象的</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>bear (情绪与感知词汇)</t>
+          <t>unbelievable (难以置信的/超乎想象的)</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>214</v>
+        <v>348</v>
       </c>
       <c r="F239" t="n">
-        <v>4.879</v>
+        <v>4.983</v>
       </c>
       <c r="G239" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>FEAR</t>
+          <t>CATE</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
         <v>4.856</v>
       </c>
       <c r="G240" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>4.892</v>
       </c>
       <c r="G243" t="n">
-        <v>0.15</v>
+        <v>0.6</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>4.613</v>
       </c>
       <c r="G244" t="n">
-        <v>-0.375</v>
+        <v>-1.5</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>favorite</t>
+          <t>lower</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -8952,21 +8952,21 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>favorite (情绪与感知词汇)</t>
+          <t>lower (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>344</v>
+        <v>130</v>
       </c>
       <c r="F251" t="n">
-        <v>4.968</v>
+        <v>4.7</v>
       </c>
       <c r="G251" t="n">
-        <v>0.5</v>
+        <v>-1.2</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>SADNESS</t>
         </is>
       </c>
     </row>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>baby</t>
+          <t>daughter</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -8986,14 +8986,14 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>baby (情绪与感知词汇)</t>
+          <t>daughter (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>40</v>
+        <v>359</v>
       </c>
       <c r="F252" t="n">
-        <v>4.725</v>
+        <v>4.889</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>daughter</t>
+          <t>baby</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9020,14 +9020,14 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>daughter (情绪与感知词汇)</t>
+          <t>baby (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>359</v>
+        <v>40</v>
       </c>
       <c r="F253" t="n">
-        <v>4.889</v>
+        <v>4.725</v>
       </c>
       <c r="G253" t="n">
         <v>0</v>
@@ -9044,7 +9044,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>lower</t>
+          <t>favorite</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9054,21 +9054,21 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>lower (情绪与感知词汇)</t>
+          <t>favorite (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>130</v>
+        <v>344</v>
       </c>
       <c r="F254" t="n">
-        <v>4.7</v>
+        <v>4.968</v>
       </c>
       <c r="G254" t="n">
-        <v>-0.3</v>
+        <v>2</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>SADNESS</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>reliable</t>
+          <t>hesitation</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9156,21 +9156,21 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>reliable (情绪与感知词汇)</t>
+          <t>hesitation (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="F257" t="n">
-        <v>4.561</v>
+        <v>4.87</v>
       </c>
       <c r="G257" t="n">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>FEAR</t>
         </is>
       </c>
     </row>
@@ -9180,7 +9180,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>hesitation</t>
+          <t>reliable</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9190,21 +9190,21 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>hesitation (情绪与感知词汇)</t>
+          <t>reliable (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="F258" t="n">
-        <v>4.87</v>
+        <v>4.561</v>
       </c>
       <c r="G258" t="n">
-        <v>-0.275</v>
+        <v>0</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>FEAR</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -9214,27 +9214,27 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>standing</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>空中悬停/飞行姿态</t>
+          <t>高度认同/一致赞同</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>standing (空中悬停/飞行姿态)</t>
+          <t>agree (高度认同/一致赞同)</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>128</v>
+        <v>72</v>
       </c>
       <c r="F259" t="n">
-        <v>4.711</v>
+        <v>4.944</v>
       </c>
       <c r="G259" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -9282,27 +9282,27 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>agree</t>
+          <t>standing</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>高度认同/一致赞同</t>
+          <t>空中悬停/飞行姿态</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>agree (高度认同/一致赞同)</t>
+          <t>standing (空中悬停/飞行姿态)</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="F261" t="n">
-        <v>4.944</v>
+        <v>4.711</v>
       </c>
       <c r="G261" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -9350,24 +9350,24 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>overcast</t>
+          <t>chatty</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>多云天色的/阴天的</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>overcast (多云天色的/阴天的)</t>
+          <t>chatty (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>110</v>
+        <v>29</v>
       </c>
       <c r="F263" t="n">
-        <v>4.745</v>
+        <v>4.897</v>
       </c>
       <c r="G263" t="n">
         <v>0</v>
@@ -9384,24 +9384,24 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>chatty</t>
+          <t>overcast</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>多云天色的/阴天的</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>chatty (情绪与感知词汇)</t>
+          <t>overcast (多云天色的/阴天的)</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>29</v>
+        <v>110</v>
       </c>
       <c r="F264" t="n">
-        <v>4.897</v>
+        <v>4.745</v>
       </c>
       <c r="G264" t="n">
         <v>0</v>
@@ -9438,7 +9438,7 @@
         <v>4.565</v>
       </c>
       <c r="G265" t="n">
-        <v>-0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>4.956</v>
       </c>
       <c r="G266" t="n">
-        <v>0.725</v>
+        <v>2.9</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>rating</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -9564,21 +9564,21 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>agreed (情绪与感知词汇)</t>
+          <t>rating (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="F269" t="n">
-        <v>4.758</v>
+        <v>4.279</v>
       </c>
       <c r="G269" t="n">
-        <v>0.275</v>
+        <v>0</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>SADNESS</t>
         </is>
       </c>
     </row>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>honesty</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -9598,17 +9598,17 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>honesty (情绪与感知词汇)</t>
+          <t>agreed (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="F270" t="n">
-        <v>4.556</v>
+        <v>4.758</v>
       </c>
       <c r="G270" t="n">
-        <v>0.55</v>
+        <v>1.1</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>honesty</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -9632,21 +9632,21 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>rating (情绪与感知词汇)</t>
+          <t>honesty (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="F271" t="n">
-        <v>4.279</v>
+        <v>4.556</v>
       </c>
       <c r="G271" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>SADNESS</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -9744,7 +9744,7 @@
         <v>4.571</v>
       </c>
       <c r="G274" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -9758,31 +9758,31 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>touched</t>
+          <t>immaculate</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>完美无瑕的</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>touched (情绪与感知词汇)</t>
+          <t>immaculate (完美无瑕的)</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="F275" t="n">
-        <v>4.905</v>
+        <v>5</v>
       </c>
       <c r="G275" t="n">
         <v>0</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>CATE</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -9792,31 +9792,31 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>immaculate</t>
+          <t>touched</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>完美无瑕的</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>immaculate (完美无瑕的)</t>
+          <t>touched (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F276" t="n">
-        <v>5</v>
+        <v>4.905</v>
       </c>
       <c r="G276" t="n">
         <v>0</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>CATE</t>
         </is>
       </c>
     </row>
@@ -9846,7 +9846,7 @@
         <v>4.944</v>
       </c>
       <c r="G277" t="n">
-        <v>0.45</v>
+        <v>1.8</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>4.965</v>
       </c>
       <c r="G280" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>majestic</t>
+          <t>luck</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -9972,17 +9972,17 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>majestic (情绪与感知词汇)</t>
+          <t>luck (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="F281" t="n">
-        <v>4.959</v>
+        <v>4.649</v>
       </c>
       <c r="G281" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>luck</t>
+          <t>majestic</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>luck (情绪与感知词汇)</t>
+          <t>majestic (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>97</v>
+        <v>193</v>
       </c>
       <c r="F282" t="n">
-        <v>4.649</v>
+        <v>4.959</v>
       </c>
       <c r="G282" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -10098,31 +10098,31 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>apprehensive</t>
+          <t>interest</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>兴趣/看点</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>apprehensive (情绪与感知词汇)</t>
+          <t>interest (兴趣/看点)</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>92</v>
+        <v>228</v>
       </c>
       <c r="F285" t="n">
-        <v>4.989</v>
+        <v>4.921</v>
       </c>
       <c r="G285" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>ANTICIPATION</t>
+          <t>CATE</t>
         </is>
       </c>
     </row>
@@ -10132,31 +10132,31 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>interest</t>
+          <t>apprehensive</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>兴趣/看点</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>interest (兴趣/看点)</t>
+          <t>apprehensive (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>228</v>
+        <v>92</v>
       </c>
       <c r="F286" t="n">
-        <v>4.921</v>
+        <v>4.989</v>
       </c>
       <c r="G286" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>CATE</t>
+          <t>ANTICIPATION</t>
         </is>
       </c>
     </row>
@@ -10234,7 +10234,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>surprisingly</t>
+          <t>fell</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -10244,21 +10244,21 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>surprisingly (情绪与感知词汇)</t>
+          <t>fell (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="F289" t="n">
-        <v>4.971</v>
+        <v>4.695</v>
       </c>
       <c r="G289" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>ANTICIPATION</t>
+          <t>SADNESS</t>
         </is>
       </c>
     </row>
@@ -10268,7 +10268,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>depth</t>
+          <t>surprisingly</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -10278,21 +10278,21 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>depth (情绪与感知词汇)</t>
+          <t>surprisingly (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F290" t="n">
-        <v>4.953</v>
+        <v>4.971</v>
       </c>
       <c r="G290" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>ANTICIPATION</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>avalanche</t>
+          <t>endless</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -10312,11 +10312,11 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>avalanche (情绪与感知词汇)</t>
+          <t>endless (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F291" t="n">
         <v>5</v>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>SADNESS</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>endless</t>
+          <t>avalanche</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -10346,11 +10346,11 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>endless (情绪与感知词汇)</t>
+          <t>avalanche (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F292" t="n">
         <v>5</v>
@@ -10360,7 +10360,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>SADNESS</t>
         </is>
       </c>
     </row>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>fell</t>
+          <t>depth</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -10380,21 +10380,21 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>fell (情绪与感知词汇)</t>
+          <t>depth (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="F293" t="n">
-        <v>4.695</v>
+        <v>4.953</v>
       </c>
       <c r="G293" t="n">
         <v>0</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>SADNESS</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -10404,31 +10404,31 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>important</t>
+          <t>forward</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>前向视角/期待视角</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>important (情绪与感知词汇)</t>
+          <t>forward (前向视角/期待视角)</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="F294" t="n">
-        <v>4.74</v>
+        <v>4.556</v>
       </c>
       <c r="G294" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>CATE</t>
         </is>
       </c>
     </row>
@@ -10438,31 +10438,31 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>forward</t>
+          <t>important</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>前向视角/期待视角</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>forward (前向视角/期待视角)</t>
+          <t>important (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="F295" t="n">
-        <v>4.556</v>
+        <v>4.74</v>
       </c>
       <c r="G295" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>CATE</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -10492,7 +10492,7 @@
         <v>4.866</v>
       </c>
       <c r="G296" t="n">
-        <v>0.275</v>
+        <v>1.1</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
         <v>4.947</v>
       </c>
       <c r="G298" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>anchorage</t>
+          <t>swim</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -10618,21 +10618,21 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>anchorage (情绪与感知词汇)</t>
+          <t>swim (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>166</v>
+        <v>17</v>
       </c>
       <c r="F300" t="n">
-        <v>4.753</v>
+        <v>4.824</v>
       </c>
       <c r="G300" t="n">
         <v>0</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>SADNESS</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>enjoying</t>
+          <t>worried</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -10652,21 +10652,21 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>enjoying (情绪与感知词汇)</t>
+          <t>worried (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="F301" t="n">
-        <v>4.867</v>
+        <v>4.87</v>
       </c>
       <c r="G301" t="n">
-        <v>0.6</v>
+        <v>-1.2</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>SADNESS</t>
         </is>
       </c>
     </row>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>worried</t>
+          <t>anchorage</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -10720,17 +10720,17 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>worried (情绪与感知词汇)</t>
+          <t>anchorage (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="F303" t="n">
-        <v>4.87</v>
+        <v>4.753</v>
       </c>
       <c r="G303" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>swim</t>
+          <t>enjoying</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -10754,17 +10754,17 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>swim (情绪与感知词汇)</t>
+          <t>enjoying (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="F304" t="n">
-        <v>4.824</v>
+        <v>4.867</v>
       </c>
       <c r="G304" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H304" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>4.95</v>
       </c>
       <c r="G307" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="H307" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>4.923</v>
       </c>
       <c r="G308" t="n">
-        <v>-0.45</v>
+        <v>-1.8</v>
       </c>
       <c r="H308" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>4.925</v>
       </c>
       <c r="G311" t="n">
-        <v>0.45</v>
+        <v>1.8</v>
       </c>
       <c r="H311" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>considerate</t>
+          <t>appreciation</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -11026,21 +11026,21 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>considerate (情绪与感知词汇)</t>
+          <t>appreciation (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="F312" t="n">
-        <v>4.967</v>
+        <v>4.98</v>
       </c>
       <c r="G312" t="n">
-        <v>0.475</v>
+        <v>2.3</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>appreciation</t>
+          <t>considerate</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -11060,21 +11060,21 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>appreciation (情绪与感知词汇)</t>
+          <t>considerate (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F313" t="n">
-        <v>4.98</v>
+        <v>4.967</v>
       </c>
       <c r="G313" t="n">
-        <v>0.575</v>
+        <v>1.9</v>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -11104,7 +11104,7 @@
         <v>4.219</v>
       </c>
       <c r="G314" t="n">
-        <v>-0.325</v>
+        <v>-1.3</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>falling</t>
+          <t>guarantee</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -11162,21 +11162,21 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>falling (情绪与感知词汇)</t>
+          <t>guarantee (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="F316" t="n">
-        <v>4.8</v>
+        <v>4.767</v>
       </c>
       <c r="G316" t="n">
-        <v>-0.15</v>
+        <v>1</v>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>SADNESS</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -11220,7 +11220,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>guarantee</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -11230,21 +11230,21 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>guarantee (情绪与感知词汇)</t>
+          <t>falling (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="F318" t="n">
-        <v>4.767</v>
+        <v>4.8</v>
       </c>
       <c r="G318" t="n">
-        <v>0.25</v>
+        <v>-0.6</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>SADNESS</t>
         </is>
       </c>
     </row>
@@ -11288,7 +11288,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>policy</t>
+          <t>communicate</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -11298,14 +11298,14 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>policy (情绪与感知词汇)</t>
+          <t>communicate (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="F320" t="n">
-        <v>4.306</v>
+        <v>4.693</v>
       </c>
       <c r="G320" t="n">
         <v>0</v>
@@ -11322,31 +11322,31 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>understanding</t>
+          <t>horrible</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>极差的/糟糕透顶的</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>understanding (情绪与感知词汇)</t>
+          <t>horrible (极差的/糟糕透顶的)</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="F321" t="n">
-        <v>4.714</v>
+        <v>2.31</v>
       </c>
       <c r="G321" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>DISGUST</t>
         </is>
       </c>
     </row>
@@ -11356,31 +11356,31 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>horrible</t>
+          <t>understanding</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>极差的/糟糕透顶的</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>horrible (极差的/糟糕透顶的)</t>
+          <t>understanding (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="F322" t="n">
-        <v>2.31</v>
+        <v>4.714</v>
       </c>
       <c r="G322" t="n">
-        <v>-0.625</v>
+        <v>0</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>DISGUST</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>communicate</t>
+          <t>policy</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -11400,14 +11400,14 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>communicate (情绪与感知词汇)</t>
+          <t>policy (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="F323" t="n">
-        <v>4.693</v>
+        <v>4.306</v>
       </c>
       <c r="G323" t="n">
         <v>0</v>
@@ -11444,7 +11444,7 @@
         <v>4.938</v>
       </c>
       <c r="G324" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>sunshine</t>
+          <t>lines</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -11468,21 +11468,21 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>sunshine (情绪与感知词汇)</t>
+          <t>lines (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="F325" t="n">
-        <v>4.815</v>
+        <v>4.816</v>
       </c>
       <c r="G325" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>FEAR</t>
         </is>
       </c>
     </row>
@@ -11492,7 +11492,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>lines</t>
+          <t>sunshine</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -11502,21 +11502,21 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>lines (情绪与感知词汇)</t>
+          <t>sunshine (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F326" t="n">
-        <v>4.816</v>
+        <v>4.815</v>
       </c>
       <c r="G326" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>FEAR</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -11546,7 +11546,7 @@
         <v>4.535</v>
       </c>
       <c r="G327" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>4.907</v>
       </c>
       <c r="G328" t="n">
-        <v>-0.175</v>
+        <v>-0.7</v>
       </c>
       <c r="H328" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>inexpensive</t>
+          <t>evident</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -11740,21 +11740,21 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>inexpensive (情绪与感知词汇)</t>
+          <t>evident (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F333" t="n">
-        <v>4.846</v>
+        <v>4.909</v>
       </c>
       <c r="G333" t="n">
         <v>0</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>CATE</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -11764,7 +11764,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>evident</t>
+          <t>inexpensive</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -11774,21 +11774,21 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>evident (情绪与感知词汇)</t>
+          <t>inexpensive (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F334" t="n">
-        <v>4.909</v>
+        <v>4.846</v>
       </c>
       <c r="G334" t="n">
         <v>0</v>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>CATE</t>
         </is>
       </c>
     </row>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>respect</t>
+          <t>charm</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -11808,21 +11808,21 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>respect (情绪与感知词汇)</t>
+          <t>charm (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F335" t="n">
-        <v>4.808</v>
+        <v>4.895</v>
       </c>
       <c r="G335" t="n">
-        <v>0.525</v>
+        <v>1.7</v>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>CATE</t>
         </is>
       </c>
     </row>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>charm</t>
+          <t>respect</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -11842,21 +11842,21 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>charm (情绪与感知词汇)</t>
+          <t>respect (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F336" t="n">
-        <v>4.895</v>
+        <v>4.808</v>
       </c>
       <c r="G336" t="n">
-        <v>0.425</v>
+        <v>2.1</v>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>CATE</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>delighted</t>
+          <t>essential</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -11876,21 +11876,21 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>delighted (情绪与感知词汇)</t>
+          <t>essential (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F337" t="n">
-        <v>5</v>
+        <v>4.875</v>
       </c>
       <c r="G337" t="n">
-        <v>0.575</v>
+        <v>0</v>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>CATE</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>essential</t>
+          <t>delighted</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -11910,21 +11910,21 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>essential (情绪与感知词汇)</t>
+          <t>delighted (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F338" t="n">
-        <v>4.875</v>
+        <v>5</v>
       </c>
       <c r="G338" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>CATE</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -11954,7 +11954,7 @@
         <v>5</v>
       </c>
       <c r="G339" t="n">
-        <v>0.55</v>
+        <v>2.2</v>
       </c>
       <c r="H339" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>4.51</v>
       </c>
       <c r="G340" t="n">
-        <v>-0.425</v>
+        <v>-1.7</v>
       </c>
       <c r="H340" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         <v>4.587</v>
       </c>
       <c r="G342" t="n">
-        <v>0.15</v>
+        <v>0.6</v>
       </c>
       <c r="H342" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>4.903</v>
       </c>
       <c r="G344" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="H344" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>3.135</v>
       </c>
       <c r="G348" t="n">
-        <v>-0.45</v>
+        <v>-1.8</v>
       </c>
       <c r="H348" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>4.369</v>
       </c>
       <c r="G349" t="n">
-        <v>0.55</v>
+        <v>2.2</v>
       </c>
       <c r="H349" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>4.924</v>
       </c>
       <c r="G354" t="n">
-        <v>0.35</v>
+        <v>1.4</v>
       </c>
       <c r="H354" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>4.971</v>
       </c>
       <c r="G356" t="n">
-        <v>-0.175</v>
+        <v>-0.7</v>
       </c>
       <c r="H356" t="inlineStr">
         <is>
@@ -12648,31 +12648,31 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>courtesy</t>
+          <t>sensational</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>轰动出色的</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>courtesy (情绪与感知词汇)</t>
+          <t>sensational (轰动出色的)</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F360" t="n">
-        <v>4.476</v>
+        <v>5</v>
       </c>
       <c r="G360" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>CATE</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -12682,31 +12682,31 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>sensational</t>
+          <t>courtesy</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>轰动出色的</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>sensational (轰动出色的)</t>
+          <t>courtesy (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E361" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F361" t="n">
-        <v>5</v>
+        <v>4.476</v>
       </c>
       <c r="G361" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>CATE</t>
         </is>
       </c>
     </row>
@@ -12736,7 +12736,7 @@
         <v>4.935</v>
       </c>
       <c r="G362" t="n">
-        <v>0.375</v>
+        <v>1.5</v>
       </c>
       <c r="H362" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>4.866</v>
       </c>
       <c r="G364" t="n">
-        <v>-0.4</v>
+        <v>-1.6</v>
       </c>
       <c r="H364" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>4.875</v>
       </c>
       <c r="G366" t="n">
-        <v>0.375</v>
+        <v>1.5</v>
       </c>
       <c r="H366" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>mail</t>
+          <t>sadly</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -12964,21 +12964,21 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>mail (情绪与感知词汇)</t>
+          <t>sadly (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E369" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F369" t="n">
-        <v>4.791</v>
+        <v>4.394</v>
       </c>
       <c r="G369" t="n">
-        <v>0</v>
+        <v>-1.8</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>ANTICIPATION</t>
+          <t>SADNESS</t>
         </is>
       </c>
     </row>
@@ -12988,7 +12988,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>sadly</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -12998,21 +12998,21 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>sadly (情绪与感知词汇)</t>
+          <t>mail (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E370" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="F370" t="n">
-        <v>4.394</v>
+        <v>4.791</v>
       </c>
       <c r="G370" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>SADNESS</t>
+          <t>ANTICIPATION</t>
         </is>
       </c>
     </row>
@@ -13178,7 +13178,7 @@
         <v>4.8</v>
       </c>
       <c r="G375" t="n">
-        <v>-0.4</v>
+        <v>-1.6</v>
       </c>
       <c r="H375" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>4.941</v>
       </c>
       <c r="G377" t="n">
-        <v>0.725</v>
+        <v>2.9</v>
       </c>
       <c r="H377" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         <v>4.967</v>
       </c>
       <c r="G381" t="n">
-        <v>0.65</v>
+        <v>2.6</v>
       </c>
       <c r="H381" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>4.958</v>
       </c>
       <c r="G385" t="n">
-        <v>0.375</v>
+        <v>1.5</v>
       </c>
       <c r="H385" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>4.946</v>
       </c>
       <c r="G386" t="n">
-        <v>0.575</v>
+        <v>2.3</v>
       </c>
       <c r="H386" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>4.949</v>
       </c>
       <c r="G387" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>5</v>
       </c>
       <c r="G389" t="n">
-        <v>0.65</v>
+        <v>2.6</v>
       </c>
       <c r="H389" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>cap</t>
+          <t>fire</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -13678,21 +13678,21 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>cap (情绪与感知词汇)</t>
+          <t>fire (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E390" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F390" t="n">
-        <v>4.947</v>
+        <v>4.781</v>
       </c>
       <c r="G390" t="n">
-        <v>0</v>
+        <v>-1.4</v>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>FEAR</t>
         </is>
       </c>
     </row>
@@ -13702,7 +13702,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>fire</t>
+          <t>cap</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -13712,21 +13712,21 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>fire (情绪与感知词汇)</t>
+          <t>cap (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E391" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F391" t="n">
-        <v>4.781</v>
+        <v>4.947</v>
       </c>
       <c r="G391" t="n">
-        <v>-0.35</v>
+        <v>0</v>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>FEAR</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -13790,7 +13790,7 @@
         <v>4.089</v>
       </c>
       <c r="G393" t="n">
-        <v>-0.3</v>
+        <v>-1.2</v>
       </c>
       <c r="H393" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>5</v>
       </c>
       <c r="G395" t="n">
-        <v>0.475</v>
+        <v>1.9</v>
       </c>
       <c r="H395" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>holiday</t>
+          <t>brother</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -13916,21 +13916,21 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>holiday (情绪与感知词汇)</t>
+          <t>brother (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E397" t="n">
-        <v>117</v>
+        <v>58</v>
       </c>
       <c r="F397" t="n">
-        <v>4.786</v>
+        <v>4.897</v>
       </c>
       <c r="G397" t="n">
-        <v>0.425</v>
+        <v>0</v>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -13940,7 +13940,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>brother</t>
+          <t>holiday</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -13950,21 +13950,21 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>brother (情绪与感知词汇)</t>
+          <t>holiday (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E398" t="n">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="F398" t="n">
-        <v>4.897</v>
+        <v>4.786</v>
       </c>
       <c r="G398" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -13994,7 +13994,7 @@
         <v>4.409</v>
       </c>
       <c r="G399" t="n">
-        <v>-0.5</v>
+        <v>-2</v>
       </c>
       <c r="H399" t="inlineStr">
         <is>
@@ -14028,7 +14028,7 @@
         <v>4.971</v>
       </c>
       <c r="G400" t="n">
-        <v>0.575</v>
+        <v>2.3</v>
       </c>
       <c r="H400" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>4.825</v>
       </c>
       <c r="G401" t="n">
-        <v>-0.225</v>
+        <v>-0.9</v>
       </c>
       <c r="H401" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>4.271</v>
       </c>
       <c r="G403" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="H403" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>4.981</v>
       </c>
       <c r="G405" t="n">
-        <v>0.475</v>
+        <v>1.9</v>
       </c>
       <c r="H405" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>4.983</v>
       </c>
       <c r="G406" t="n">
-        <v>0.65</v>
+        <v>2.6</v>
       </c>
       <c r="H406" t="inlineStr">
         <is>
@@ -14300,7 +14300,7 @@
         <v>4.965</v>
       </c>
       <c r="G408" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>4.955</v>
       </c>
       <c r="G409" t="n">
-        <v>0.575</v>
+        <v>2.3</v>
       </c>
       <c r="H409" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>3.118</v>
       </c>
       <c r="G411" t="n">
-        <v>-0.3</v>
+        <v>-1.2</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>3.643</v>
       </c>
       <c r="G419" t="n">
-        <v>-0.325</v>
+        <v>-1.3</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>5</v>
       </c>
       <c r="G420" t="n">
-        <v>0.625</v>
+        <v>2.5</v>
       </c>
       <c r="H420" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         <v>4.8</v>
       </c>
       <c r="G427" t="n">
-        <v>-0.35</v>
+        <v>-1.4</v>
       </c>
       <c r="H427" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
         <v>4.8</v>
       </c>
       <c r="G432" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H432" t="inlineStr">
         <is>
@@ -15130,7 +15130,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>instructions</t>
+          <t>extensive</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -15140,21 +15140,21 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>instructions (情绪与感知词汇)</t>
+          <t>extensive (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E433" t="n">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="F433" t="n">
-        <v>4.709</v>
+        <v>4.897</v>
       </c>
       <c r="G433" t="n">
         <v>0</v>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>CATE</t>
         </is>
       </c>
     </row>
@@ -15164,7 +15164,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>extensive</t>
+          <t>instructions</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -15174,21 +15174,21 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>extensive (情绪与感知词汇)</t>
+          <t>instructions (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E434" t="n">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="F434" t="n">
-        <v>4.897</v>
+        <v>4.709</v>
       </c>
       <c r="G434" t="n">
         <v>0</v>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>CATE</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -15218,7 +15218,7 @@
         <v>4.8</v>
       </c>
       <c r="G435" t="n">
-        <v>0.425</v>
+        <v>1.7</v>
       </c>
       <c r="H435" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>4.775</v>
       </c>
       <c r="G436" t="n">
-        <v>0.225</v>
+        <v>0.9</v>
       </c>
       <c r="H436" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>4.86</v>
       </c>
       <c r="G437" t="n">
-        <v>0.35</v>
+        <v>1.4</v>
       </c>
       <c r="H437" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>4.955</v>
       </c>
       <c r="G438" t="n">
-        <v>0.575</v>
+        <v>2.3</v>
       </c>
       <c r="H438" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>5</v>
       </c>
       <c r="G439" t="n">
-        <v>0.55</v>
+        <v>2.2</v>
       </c>
       <c r="H439" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>4.987</v>
       </c>
       <c r="G440" t="n">
-        <v>0.625</v>
+        <v>2.5</v>
       </c>
       <c r="H440" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>break</t>
+          <t>elevation</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -15446,21 +15446,21 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>break (情绪与感知词汇)</t>
+          <t>elevation (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E442" t="n">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="F442" t="n">
-        <v>4.795</v>
+        <v>4.727</v>
       </c>
       <c r="G442" t="n">
         <v>0</v>
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>SURPRISE</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -15490,7 +15490,7 @@
         <v>4.97</v>
       </c>
       <c r="G443" t="n">
-        <v>0.725</v>
+        <v>2.9</v>
       </c>
       <c r="H443" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>elevation</t>
+          <t>break</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -15514,21 +15514,21 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>elevation (情绪与感知词汇)</t>
+          <t>break (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E444" t="n">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="F444" t="n">
-        <v>4.727</v>
+        <v>4.795</v>
       </c>
       <c r="G444" t="n">
         <v>0</v>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>SURPRISE</t>
         </is>
       </c>
     </row>
@@ -15558,7 +15558,7 @@
         <v>4.95</v>
       </c>
       <c r="G445" t="n">
-        <v>0.675</v>
+        <v>2.7</v>
       </c>
       <c r="H445" t="inlineStr">
         <is>
@@ -15640,31 +15640,31 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>capture</t>
+          <t>pride</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>捕捉照片/定格瞬间</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>capture (捕捉照片/定格瞬间)</t>
+          <t>pride (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E448" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F448" t="n">
-        <v>4.84</v>
+        <v>4.908</v>
       </c>
       <c r="G448" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>CATE</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -15674,7 +15674,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>pride</t>
+          <t>honeymoon</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -15684,17 +15684,17 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>pride (情绪与感知词汇)</t>
+          <t>honeymoon (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E449" t="n">
-        <v>76</v>
+        <v>181</v>
       </c>
       <c r="F449" t="n">
-        <v>4.908</v>
+        <v>5</v>
       </c>
       <c r="G449" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="H449" t="inlineStr">
         <is>
@@ -15708,31 +15708,31 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>honeymoon</t>
+          <t>capture</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>捕捉照片/定格瞬间</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>honeymoon (情绪与感知词汇)</t>
+          <t>capture (捕捉照片/定格瞬间)</t>
         </is>
       </c>
       <c r="E450" t="n">
-        <v>181</v>
+        <v>81</v>
       </c>
       <c r="F450" t="n">
-        <v>5</v>
+        <v>4.84</v>
       </c>
       <c r="G450" t="n">
         <v>0</v>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>CATE</t>
         </is>
       </c>
     </row>
@@ -15932,7 +15932,7 @@
         <v>4.95</v>
       </c>
       <c r="G456" t="n">
-        <v>0.475</v>
+        <v>1.9</v>
       </c>
       <c r="H456" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>4.95</v>
       </c>
       <c r="G457" t="n">
-        <v>0.45</v>
+        <v>1.8</v>
       </c>
       <c r="H457" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>4.143</v>
       </c>
       <c r="G458" t="n">
-        <v>-0.35</v>
+        <v>-1.4</v>
       </c>
       <c r="H458" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>4.12</v>
       </c>
       <c r="G463" t="n">
-        <v>-0.525</v>
+        <v>-2.1</v>
       </c>
       <c r="H463" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>5</v>
       </c>
       <c r="G465" t="n">
-        <v>0.75</v>
+        <v>3</v>
       </c>
       <c r="H465" t="inlineStr">
         <is>
@@ -16340,7 +16340,7 @@
         <v>4.957</v>
       </c>
       <c r="G468" t="n">
-        <v>0.55</v>
+        <v>2.2</v>
       </c>
       <c r="H468" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>ultimately</t>
+          <t>thrilling</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -16398,21 +16398,21 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>ultimately (情绪与感知词汇)</t>
+          <t>thrilling (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E470" t="n">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="F470" t="n">
-        <v>4.536</v>
+        <v>4.959</v>
       </c>
       <c r="G470" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>ANTICIPATION</t>
+          <t>JOY</t>
         </is>
       </c>
     </row>
@@ -16422,7 +16422,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>thrilling</t>
+          <t>ultimately</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -16432,21 +16432,21 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>thrilling (情绪与感知词汇)</t>
+          <t>ultimately (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E471" t="n">
-        <v>145</v>
+        <v>28</v>
       </c>
       <c r="F471" t="n">
-        <v>4.959</v>
+        <v>4.536</v>
       </c>
       <c r="G471" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>JOY</t>
+          <t>ANTICIPATION</t>
         </is>
       </c>
     </row>
@@ -16476,7 +16476,7 @@
         <v>4.767</v>
       </c>
       <c r="G472" t="n">
-        <v>0.575</v>
+        <v>2.3</v>
       </c>
       <c r="H472" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>5</v>
       </c>
       <c r="G473" t="n">
-        <v>-0.3</v>
+        <v>-1.2</v>
       </c>
       <c r="H473" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>5</v>
       </c>
       <c r="G474" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H474" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>4.731</v>
       </c>
       <c r="G475" t="n">
-        <v>0.325</v>
+        <v>1.3</v>
       </c>
       <c r="H475" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>4.917</v>
       </c>
       <c r="G477" t="n">
-        <v>0.275</v>
+        <v>1.1</v>
       </c>
       <c r="H477" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>crazy</t>
+          <t>upset</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -16670,17 +16670,17 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>crazy (情绪与感知词汇)</t>
+          <t>upset (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E478" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="F478" t="n">
-        <v>4.76</v>
+        <v>3.478</v>
       </c>
       <c r="G478" t="n">
-        <v>-0.35</v>
+        <v>-1.6</v>
       </c>
       <c r="H478" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>upset</t>
+          <t>witness</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -16704,21 +16704,21 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>upset (情绪与感知词汇)</t>
+          <t>witness (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E479" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F479" t="n">
-        <v>3.478</v>
+        <v>5</v>
       </c>
       <c r="G479" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>SADNESS</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -16728,7 +16728,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>witness</t>
+          <t>crazy</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -16738,21 +16738,21 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>witness (情绪与感知词汇)</t>
+          <t>crazy (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E480" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="F480" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="G480" t="n">
-        <v>0</v>
+        <v>-1.4</v>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>SADNESS</t>
         </is>
       </c>
     </row>
@@ -16816,7 +16816,7 @@
         <v>4.875</v>
       </c>
       <c r="G482" t="n">
-        <v>0.375</v>
+        <v>1.5</v>
       </c>
       <c r="H482" t="inlineStr">
         <is>
@@ -16884,7 +16884,7 @@
         <v>4.846</v>
       </c>
       <c r="G484" t="n">
-        <v>0.35</v>
+        <v>1.4</v>
       </c>
       <c r="H484" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>4.912</v>
       </c>
       <c r="G485" t="n">
-        <v>0.575</v>
+        <v>2.3</v>
       </c>
       <c r="H485" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>4.983</v>
       </c>
       <c r="G486" t="n">
-        <v>0.55</v>
+        <v>2.2</v>
       </c>
       <c r="H486" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>4.902</v>
       </c>
       <c r="G490" t="n">
-        <v>0.625</v>
+        <v>2.5</v>
       </c>
       <c r="H490" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>4.761</v>
       </c>
       <c r="G492" t="n">
-        <v>-0.275</v>
+        <v>-1.1</v>
       </c>
       <c r="H492" t="inlineStr">
         <is>
@@ -17170,7 +17170,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>taught</t>
+          <t>questionable</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -17180,21 +17180,21 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>taught (情绪与感知词汇)</t>
+          <t>questionable (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E493" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F493" t="n">
-        <v>5</v>
+        <v>4.842</v>
       </c>
       <c r="G493" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>DISGUST</t>
         </is>
       </c>
     </row>
@@ -17238,7 +17238,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>taught</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -17248,21 +17248,21 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>questionable (情绪与感知词汇)</t>
+          <t>taught (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E495" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F495" t="n">
-        <v>4.842</v>
+        <v>5</v>
       </c>
       <c r="G495" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>DISGUST</t>
+          <t>TRUST</t>
         </is>
       </c>
     </row>
@@ -17292,7 +17292,7 @@
         <v>4.611</v>
       </c>
       <c r="G496" t="n">
-        <v>-0.425</v>
+        <v>-1.7</v>
       </c>
       <c r="H496" t="inlineStr">
         <is>
@@ -17326,7 +17326,7 @@
         <v>4</v>
       </c>
       <c r="G497" t="n">
-        <v>-0.575</v>
+        <v>-2.3</v>
       </c>
       <c r="H497" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>4.32</v>
       </c>
       <c r="G500" t="n">
-        <v>-0.7</v>
+        <v>-2.8</v>
       </c>
       <c r="H500" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>4.5</v>
       </c>
       <c r="G502" t="n">
-        <v>0.075</v>
+        <v>0.3</v>
       </c>
       <c r="H502" t="inlineStr">
         <is>
@@ -17598,7 +17598,7 @@
         <v>4.667</v>
       </c>
       <c r="G505" t="n">
-        <v>-0.425</v>
+        <v>-1.7</v>
       </c>
       <c r="H505" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>4.5</v>
       </c>
       <c r="G509" t="n">
-        <v>-0.475</v>
+        <v>-1.9</v>
       </c>
       <c r="H509" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>boy</t>
+          <t>spur</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -17792,21 +17792,21 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>boy (情绪与感知词汇)</t>
+          <t>spur (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E511" t="n">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="F511" t="n">
-        <v>4.951</v>
+        <v>4.944</v>
       </c>
       <c r="G511" t="n">
         <v>0</v>
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>DISGUST</t>
+          <t>FEAR</t>
         </is>
       </c>
     </row>
@@ -17816,7 +17816,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>spur</t>
+          <t>boy</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -17826,21 +17826,21 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>spur (情绪与感知词汇)</t>
+          <t>boy (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E512" t="n">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="F512" t="n">
-        <v>4.944</v>
+        <v>4.951</v>
       </c>
       <c r="G512" t="n">
         <v>0</v>
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>FEAR</t>
+          <t>DISGUST</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
         <v>4.95</v>
       </c>
       <c r="G515" t="n">
-        <v>0.425</v>
+        <v>1.7</v>
       </c>
       <c r="H515" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>4.933</v>
       </c>
       <c r="G518" t="n">
-        <v>-0.6</v>
+        <v>-2.4</v>
       </c>
       <c r="H518" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>4.968</v>
       </c>
       <c r="G519" t="n">
-        <v>0.75</v>
+        <v>3</v>
       </c>
       <c r="H519" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>praise</t>
+          <t>unexpected</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -18200,17 +18200,17 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>praise (情绪与感知词汇)</t>
+          <t>unexpected (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E523" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="F523" t="n">
-        <v>4.933</v>
+        <v>4.9</v>
       </c>
       <c r="G523" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="H523" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>enthusiasm</t>
+          <t>praise</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -18234,17 +18234,17 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>enthusiasm (情绪与感知词汇)</t>
+          <t>praise (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E524" t="n">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="F524" t="n">
-        <v>4.923</v>
+        <v>4.933</v>
       </c>
       <c r="G524" t="n">
-        <v>0.475</v>
+        <v>2.6</v>
       </c>
       <c r="H524" t="inlineStr">
         <is>
@@ -18258,7 +18258,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>unexpected</t>
+          <t>enthusiasm</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -18268,17 +18268,17 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>unexpected (情绪与感知词汇)</t>
+          <t>enthusiasm (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E525" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F525" t="n">
-        <v>4.9</v>
+        <v>4.923</v>
       </c>
       <c r="G525" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="H525" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>4.938</v>
       </c>
       <c r="G526" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="H526" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>4.556</v>
       </c>
       <c r="G529" t="n">
-        <v>0.525</v>
+        <v>2.1</v>
       </c>
       <c r="H529" t="inlineStr">
         <is>
@@ -18584,7 +18584,7 @@
         <v>4.871</v>
       </c>
       <c r="G534" t="n">
-        <v>0.675</v>
+        <v>2.7</v>
       </c>
       <c r="H534" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
         <v>5</v>
       </c>
       <c r="G535" t="n">
-        <v>0.675</v>
+        <v>2.7</v>
       </c>
       <c r="H535" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>5</v>
       </c>
       <c r="G542" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="H542" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>4.931</v>
       </c>
       <c r="G544" t="n">
-        <v>-0.725</v>
+        <v>-2.9</v>
       </c>
       <c r="H544" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>4.125</v>
       </c>
       <c r="G545" t="n">
-        <v>-0.425</v>
+        <v>-1.7</v>
       </c>
       <c r="H545" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>4.989</v>
       </c>
       <c r="G546" t="n">
-        <v>0.35</v>
+        <v>1.4</v>
       </c>
       <c r="H546" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>5</v>
       </c>
       <c r="G547" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="H547" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>4.75</v>
       </c>
       <c r="G548" t="n">
-        <v>0.475</v>
+        <v>1.9</v>
       </c>
       <c r="H548" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>4.862</v>
       </c>
       <c r="G550" t="n">
-        <v>0.175</v>
+        <v>0.7</v>
       </c>
       <c r="H550" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>5</v>
       </c>
       <c r="G555" t="n">
-        <v>0.55</v>
+        <v>2.2</v>
       </c>
       <c r="H555" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>4.953</v>
       </c>
       <c r="G556" t="n">
-        <v>0.725</v>
+        <v>2.9</v>
       </c>
       <c r="H556" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>4.95</v>
       </c>
       <c r="G557" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="H557" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>4.778</v>
       </c>
       <c r="G558" t="n">
-        <v>0.675</v>
+        <v>2.7</v>
       </c>
       <c r="H558" t="inlineStr">
         <is>
@@ -19536,7 +19536,7 @@
         <v>4.4</v>
       </c>
       <c r="G562" t="n">
-        <v>0.35</v>
+        <v>1.4</v>
       </c>
       <c r="H562" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>4.975</v>
       </c>
       <c r="G563" t="n">
-        <v>0.725</v>
+        <v>2.9</v>
       </c>
       <c r="H563" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>5</v>
       </c>
       <c r="G568" t="n">
-        <v>0.525</v>
+        <v>2.1</v>
       </c>
       <c r="H568" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>4.963</v>
       </c>
       <c r="G569" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H569" t="inlineStr">
         <is>
@@ -19808,7 +19808,7 @@
         <v>5</v>
       </c>
       <c r="G570" t="n">
-        <v>0.425</v>
+        <v>1.7</v>
       </c>
       <c r="H570" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>4.738</v>
       </c>
       <c r="G571" t="n">
-        <v>-0.3</v>
+        <v>-1.2</v>
       </c>
       <c r="H571" t="inlineStr">
         <is>
@@ -19890,24 +19890,24 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>leisurely</t>
+          <t>soak</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>悠闲从容的</t>
+          <t>情绪与感知词汇</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>leisurely (悠闲从容的)</t>
+          <t>soak (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E573" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F573" t="n">
-        <v>4.944</v>
+        <v>4.957</v>
       </c>
       <c r="G573" t="n">
         <v>0</v>
@@ -19924,24 +19924,24 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>soak</t>
+          <t>leisurely</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>情绪与感知词汇</t>
+          <t>悠闲从容的</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>soak (情绪与感知词汇)</t>
+          <t>leisurely (悠闲从容的)</t>
         </is>
       </c>
       <c r="E574" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F574" t="n">
-        <v>4.957</v>
+        <v>4.944</v>
       </c>
       <c r="G574" t="n">
         <v>0</v>
@@ -20012,7 +20012,7 @@
         <v>4.562</v>
       </c>
       <c r="G576" t="n">
-        <v>-0.35</v>
+        <v>-1.4</v>
       </c>
       <c r="H576" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>4.667</v>
       </c>
       <c r="G577" t="n">
-        <v>-0.6</v>
+        <v>-2.4</v>
       </c>
       <c r="H577" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>2.944</v>
       </c>
       <c r="G581" t="n">
-        <v>-0.525</v>
+        <v>-2.1</v>
       </c>
       <c r="H581" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>4.467</v>
       </c>
       <c r="G582" t="n">
-        <v>-0.525</v>
+        <v>-2.1</v>
       </c>
       <c r="H582" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>4.478</v>
       </c>
       <c r="G585" t="n">
-        <v>-0.425</v>
+        <v>-1.7</v>
       </c>
       <c r="H585" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>4.5</v>
       </c>
       <c r="G586" t="n">
-        <v>0.225</v>
+        <v>0.9</v>
       </c>
       <c r="H586" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>4.412</v>
       </c>
       <c r="G589" t="n">
-        <v>-0.45</v>
+        <v>-1.8</v>
       </c>
       <c r="H589" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>4.828</v>
       </c>
       <c r="G592" t="n">
-        <v>0.425</v>
+        <v>1.7</v>
       </c>
       <c r="H592" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>4.946</v>
       </c>
       <c r="G594" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="H594" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>4.167</v>
       </c>
       <c r="G595" t="n">
-        <v>-0.525</v>
+        <v>-2.1</v>
       </c>
       <c r="H595" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>4.933</v>
       </c>
       <c r="G596" t="n">
-        <v>0.025</v>
+        <v>0.1</v>
       </c>
       <c r="H596" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>4.636</v>
       </c>
       <c r="G602" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
       <c r="H602" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>4.765</v>
       </c>
       <c r="G604" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
       <c r="H604" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>5</v>
       </c>
       <c r="G605" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="H605" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>4.8</v>
       </c>
       <c r="G607" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="H607" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>4.667</v>
       </c>
       <c r="G611" t="n">
-        <v>0.475</v>
+        <v>1.9</v>
       </c>
       <c r="H611" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>4.514</v>
       </c>
       <c r="G612" t="n">
-        <v>-0.35</v>
+        <v>-1.4</v>
       </c>
       <c r="H612" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>tough</t>
+          <t>suffer</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -21260,21 +21260,21 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>tough (情绪与感知词汇)</t>
+          <t>suffer (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E613" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F613" t="n">
-        <v>4.5</v>
+        <v>4.941</v>
       </c>
       <c r="G613" t="n">
-        <v>-0.125</v>
+        <v>-2.5</v>
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>SADNESS</t>
+          <t>CATE</t>
         </is>
       </c>
     </row>
@@ -21284,7 +21284,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>suffer</t>
+          <t>tough</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -21294,21 +21294,21 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>suffer (情绪与感知词汇)</t>
+          <t>tough (情绪与感知词汇)</t>
         </is>
       </c>
       <c r="E614" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F614" t="n">
-        <v>4.941</v>
+        <v>4.5</v>
       </c>
       <c r="G614" t="n">
-        <v>-0.625</v>
+        <v>-0.5</v>
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>CATE</t>
+          <t>SADNESS</t>
         </is>
       </c>
     </row>
@@ -21338,7 +21338,7 @@
         <v>4.96</v>
       </c>
       <c r="G615" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="H615" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>4.87</v>
       </c>
       <c r="G616" t="n">
-        <v>-0.35</v>
+        <v>-1.4</v>
       </c>
       <c r="H616" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>4.769</v>
       </c>
       <c r="G622" t="n">
-        <v>0.375</v>
+        <v>1.5</v>
       </c>
       <c r="H622" t="inlineStr">
         <is>
@@ -21644,7 +21644,7 @@
         <v>4.821</v>
       </c>
       <c r="G624" t="n">
-        <v>0.375</v>
+        <v>1.5</v>
       </c>
       <c r="H624" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>5</v>
       </c>
       <c r="G625" t="n">
-        <v>0.625</v>
+        <v>2.5</v>
       </c>
       <c r="H625" t="inlineStr">
         <is>
